--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (4)\libsys\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (4)\libsys\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074AB5A3-5705-4D4C-AA51-53E4FA913AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5ABC3C-0E35-445F-BFAE-D84267D15D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1320,18 +1320,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1341,16 +1342,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1362,6 +1359,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1382,25 +1382,42 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1413,23 +1430,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1462,6 +1462,10 @@
     <xf numFmtId="0" fontId="11" fillId="20" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1472,10 +1476,6 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2090,7 +2090,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -2329,230 +2329,10 @@
             <a:buFont typeface="Times New Roman"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:ea typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-              <a:sym typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>Republic of the Philippines</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:schemeClr val="dk1"/>
-            </a:buClr>
-            <a:buSzPts val="2000"/>
-            <a:buFont typeface="Times New Roman"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:ea typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-              <a:sym typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>BATANGAS STATE UNIVERSITY</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:srgbClr val="FF0000"/>
-            </a:buClr>
-            <a:buSzPts val="1600"/>
-            <a:buFont typeface="Arial"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-              <a:sym typeface="Arial"/>
-            </a:rPr>
-            <a:t>The National Engineering University</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:schemeClr val="dk1"/>
-            </a:buClr>
-            <a:buSzPts val="1200"/>
-            <a:buFont typeface="Times New Roman"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:ea typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-              <a:sym typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>Lipa Campus</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:schemeClr val="dk1"/>
-            </a:buClr>
-            <a:buSzPts val="1200"/>
-            <a:buFont typeface="Times New Roman"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:ea typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-              <a:sym typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>A.Tanco Drive, Marawoy, Lipa City, Batangas, Philippines 4217</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:schemeClr val="dk1"/>
-            </a:buClr>
-            <a:buSzPts val="1000"/>
-            <a:buFont typeface="Times New Roman"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:ea typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-              <a:sym typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>Tel Nos.: (+63 43) 980-0385; 980-0387; 980-0392 to 94 loc. 3110</a:t>
-          </a:r>
-          <a:endParaRPr sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClr>
-              <a:schemeClr val="dk1"/>
-            </a:buClr>
-            <a:buSzPts val="1000"/>
-            <a:buFont typeface="Times New Roman"/>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:ea typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-              <a:sym typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>Email Address: library.lipa@g.batstate-u.edu.ph | Website Address: http://www.batstate-u.edu.ph</a:t>
-          </a:r>
           <a:endParaRPr sz="1400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1333500" cy="1257300"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.png" title="Image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
@@ -2897,255 +2677,255 @@
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1">
       <c r="A2" s="85"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
-      <c r="Y2" s="72"/>
-      <c r="Z2" s="72"/>
-      <c r="AA2" s="72"/>
-      <c r="AB2" s="72"/>
-      <c r="AC2" s="72"/>
-      <c r="AD2" s="72"/>
-      <c r="AE2" s="72"/>
-      <c r="AF2" s="72"/>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
+      <c r="W2" s="73"/>
+      <c r="X2" s="73"/>
+      <c r="Y2" s="73"/>
+      <c r="Z2" s="73"/>
+      <c r="AA2" s="73"/>
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="73"/>
+      <c r="AD2" s="73"/>
+      <c r="AE2" s="73"/>
+      <c r="AF2" s="73"/>
+      <c r="AG2" s="73"/>
+      <c r="AH2" s="73"/>
     </row>
     <row r="3" spans="1:34" ht="15" customHeight="1">
       <c r="A3" s="85"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="73"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="73"/>
+      <c r="AD3" s="73"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73"/>
+      <c r="AH3" s="73"/>
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1">
       <c r="A4" s="85"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
-      <c r="U4" s="72"/>
-      <c r="V4" s="72"/>
-      <c r="W4" s="72"/>
-      <c r="X4" s="72"/>
-      <c r="Y4" s="72"/>
-      <c r="Z4" s="72"/>
-      <c r="AA4" s="72"/>
-      <c r="AB4" s="72"/>
-      <c r="AC4" s="72"/>
-      <c r="AD4" s="72"/>
-      <c r="AE4" s="72"/>
-      <c r="AF4" s="72"/>
-      <c r="AG4" s="72"/>
-      <c r="AH4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
+      <c r="Y4" s="73"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="73"/>
+      <c r="AC4" s="73"/>
+      <c r="AD4" s="73"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="85"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="72"/>
-      <c r="U5" s="72"/>
-      <c r="V5" s="72"/>
-      <c r="W5" s="72"/>
-      <c r="X5" s="72"/>
-      <c r="Y5" s="72"/>
-      <c r="Z5" s="72"/>
-      <c r="AA5" s="72"/>
-      <c r="AB5" s="72"/>
-      <c r="AC5" s="72"/>
-      <c r="AD5" s="72"/>
-      <c r="AE5" s="72"/>
-      <c r="AF5" s="72"/>
-      <c r="AG5" s="72"/>
-      <c r="AH5" s="72"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="73"/>
+      <c r="V5" s="73"/>
+      <c r="W5" s="73"/>
+      <c r="X5" s="73"/>
+      <c r="Y5" s="73"/>
+      <c r="Z5" s="73"/>
+      <c r="AA5" s="73"/>
+      <c r="AB5" s="73"/>
+      <c r="AC5" s="73"/>
+      <c r="AD5" s="73"/>
+      <c r="AE5" s="73"/>
+      <c r="AF5" s="73"/>
+      <c r="AG5" s="73"/>
+      <c r="AH5" s="73"/>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="85"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="72"/>
-      <c r="V6" s="72"/>
-      <c r="W6" s="72"/>
-      <c r="X6" s="72"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="72"/>
-      <c r="AA6" s="72"/>
-      <c r="AB6" s="72"/>
-      <c r="AC6" s="72"/>
-      <c r="AD6" s="72"/>
-      <c r="AE6" s="72"/>
-      <c r="AF6" s="72"/>
-      <c r="AG6" s="72"/>
-      <c r="AH6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="73"/>
+      <c r="Z6" s="73"/>
+      <c r="AA6" s="73"/>
+      <c r="AB6" s="73"/>
+      <c r="AC6" s="73"/>
+      <c r="AD6" s="73"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="73"/>
+      <c r="AG6" s="73"/>
+      <c r="AH6" s="73"/>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="85"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
-      <c r="T7" s="72"/>
-      <c r="U7" s="72"/>
-      <c r="V7" s="72"/>
-      <c r="W7" s="72"/>
-      <c r="X7" s="72"/>
-      <c r="Y7" s="72"/>
-      <c r="Z7" s="72"/>
-      <c r="AA7" s="72"/>
-      <c r="AB7" s="72"/>
-      <c r="AC7" s="72"/>
-      <c r="AD7" s="72"/>
-      <c r="AE7" s="72"/>
-      <c r="AF7" s="72"/>
-      <c r="AG7" s="72"/>
-      <c r="AH7" s="72"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="73"/>
+      <c r="S7" s="73"/>
+      <c r="T7" s="73"/>
+      <c r="U7" s="73"/>
+      <c r="V7" s="73"/>
+      <c r="W7" s="73"/>
+      <c r="X7" s="73"/>
+      <c r="Y7" s="73"/>
+      <c r="Z7" s="73"/>
+      <c r="AA7" s="73"/>
+      <c r="AB7" s="73"/>
+      <c r="AC7" s="73"/>
+      <c r="AD7" s="73"/>
+      <c r="AE7" s="73"/>
+      <c r="AF7" s="73"/>
+      <c r="AG7" s="73"/>
+      <c r="AH7" s="73"/>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="85"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="72"/>
-      <c r="X8" s="72"/>
-      <c r="Y8" s="72"/>
-      <c r="Z8" s="72"/>
-      <c r="AA8" s="72"/>
-      <c r="AB8" s="72"/>
-      <c r="AC8" s="72"/>
-      <c r="AD8" s="72"/>
-      <c r="AE8" s="72"/>
-      <c r="AF8" s="72"/>
-      <c r="AG8" s="72"/>
-      <c r="AH8" s="72"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="73"/>
+      <c r="S8" s="73"/>
+      <c r="T8" s="73"/>
+      <c r="U8" s="73"/>
+      <c r="V8" s="73"/>
+      <c r="W8" s="73"/>
+      <c r="X8" s="73"/>
+      <c r="Y8" s="73"/>
+      <c r="Z8" s="73"/>
+      <c r="AA8" s="73"/>
+      <c r="AB8" s="73"/>
+      <c r="AC8" s="73"/>
+      <c r="AD8" s="73"/>
+      <c r="AE8" s="73"/>
+      <c r="AF8" s="73"/>
+      <c r="AG8" s="73"/>
+      <c r="AH8" s="73"/>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="1"/>
@@ -3187,121 +2967,121 @@
       <c r="A10" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="72"/>
-      <c r="AB10" s="72"/>
-      <c r="AC10" s="72"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="73"/>
+      <c r="T10" s="73"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="73"/>
+      <c r="AC10" s="73"/>
+      <c r="AD10" s="73"/>
+      <c r="AE10" s="73"/>
+      <c r="AF10" s="73"/>
+      <c r="AG10" s="73"/>
       <c r="AH10" s="2"/>
     </row>
     <row r="11" spans="1:34" ht="39.75" customHeight="1">
       <c r="A11" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="72"/>
-      <c r="AB11" s="72"/>
-      <c r="AC11" s="72"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="72"/>
-      <c r="AF11" s="72"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
+      <c r="Q11" s="73"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="73"/>
+      <c r="T11" s="73"/>
+      <c r="U11" s="73"/>
+      <c r="V11" s="73"/>
+      <c r="W11" s="73"/>
+      <c r="X11" s="73"/>
+      <c r="Y11" s="73"/>
+      <c r="Z11" s="73"/>
+      <c r="AA11" s="73"/>
+      <c r="AB11" s="73"/>
+      <c r="AC11" s="73"/>
+      <c r="AD11" s="73"/>
+      <c r="AE11" s="73"/>
+      <c r="AF11" s="73"/>
+      <c r="AG11" s="73"/>
+      <c r="AH11" s="73"/>
     </row>
     <row r="12" spans="1:34" ht="32.25" customHeight="1">
       <c r="A12" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="77"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="77"/>
-      <c r="X12" s="77"/>
-      <c r="Y12" s="77"/>
-      <c r="Z12" s="77"/>
-      <c r="AA12" s="77"/>
-      <c r="AB12" s="77"/>
-      <c r="AC12" s="77"/>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="77"/>
-      <c r="AF12" s="77"/>
-      <c r="AG12" s="77"/>
-      <c r="AH12" s="68"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+      <c r="Q12" s="70"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="70"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="70"/>
+      <c r="V12" s="70"/>
+      <c r="W12" s="70"/>
+      <c r="X12" s="70"/>
+      <c r="Y12" s="70"/>
+      <c r="Z12" s="70"/>
+      <c r="AA12" s="70"/>
+      <c r="AB12" s="70"/>
+      <c r="AC12" s="70"/>
+      <c r="AD12" s="70"/>
+      <c r="AE12" s="70"/>
+      <c r="AF12" s="70"/>
+      <c r="AG12" s="70"/>
+      <c r="AH12" s="66"/>
     </row>
     <row r="13" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="3">
         <v>1</v>
       </c>
@@ -3400,7 +3180,7 @@
       </c>
     </row>
     <row r="14" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="82" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -3505,7 +3285,7 @@
       </c>
     </row>
     <row r="15" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A15" s="66"/>
+      <c r="A15" s="68"/>
       <c r="B15" s="5" t="s">
         <v>7</v>
       </c>
@@ -3647,45 +3427,45 @@
       <c r="A17" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="77"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77"/>
-      <c r="S17" s="77"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="77"/>
-      <c r="V17" s="77"/>
-      <c r="W17" s="77"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="77"/>
-      <c r="Z17" s="77"/>
-      <c r="AA17" s="77"/>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="77"/>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="77"/>
-      <c r="AF17" s="77"/>
-      <c r="AG17" s="77"/>
-      <c r="AH17" s="68"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="70"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="66"/>
     </row>
     <row r="18" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="68"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="3">
         <v>1</v>
       </c>
@@ -3784,7 +3564,7 @@
       </c>
     </row>
     <row r="19" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="82" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -3889,7 +3669,7 @@
       </c>
     </row>
     <row r="20" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A20" s="66"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
@@ -4031,45 +3811,45 @@
       <c r="A22" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="77"/>
-      <c r="Q22" s="77"/>
-      <c r="R22" s="77"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="77"/>
-      <c r="U22" s="77"/>
-      <c r="V22" s="77"/>
-      <c r="W22" s="77"/>
-      <c r="X22" s="77"/>
-      <c r="Y22" s="77"/>
-      <c r="Z22" s="77"/>
-      <c r="AA22" s="77"/>
-      <c r="AB22" s="77"/>
-      <c r="AC22" s="77"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="77"/>
-      <c r="AF22" s="77"/>
-      <c r="AG22" s="77"/>
-      <c r="AH22" s="68"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="70"/>
+      <c r="T22" s="70"/>
+      <c r="U22" s="70"/>
+      <c r="V22" s="70"/>
+      <c r="W22" s="70"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="70"/>
+      <c r="AB22" s="70"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="66"/>
     </row>
     <row r="23" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="68"/>
+      <c r="B23" s="66"/>
       <c r="C23" s="3">
         <v>1</v>
       </c>
@@ -4168,7 +3948,7 @@
       </c>
     </row>
     <row r="24" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="82" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -4273,7 +4053,7 @@
       </c>
     </row>
     <row r="25" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A25" s="66"/>
+      <c r="A25" s="68"/>
       <c r="B25" s="5" t="s">
         <v>7</v>
       </c>
@@ -4415,45 +4195,45 @@
       <c r="A27" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77"/>
-      <c r="M27" s="77"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="77"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
-      <c r="R27" s="77"/>
-      <c r="S27" s="77"/>
-      <c r="T27" s="77"/>
-      <c r="U27" s="77"/>
-      <c r="V27" s="77"/>
-      <c r="W27" s="77"/>
-      <c r="X27" s="77"/>
-      <c r="Y27" s="77"/>
-      <c r="Z27" s="77"/>
-      <c r="AA27" s="77"/>
-      <c r="AB27" s="77"/>
-      <c r="AC27" s="77"/>
-      <c r="AD27" s="77"/>
-      <c r="AE27" s="77"/>
-      <c r="AF27" s="77"/>
-      <c r="AG27" s="77"/>
-      <c r="AH27" s="68"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="70"/>
+      <c r="S27" s="70"/>
+      <c r="T27" s="70"/>
+      <c r="U27" s="70"/>
+      <c r="V27" s="70"/>
+      <c r="W27" s="70"/>
+      <c r="X27" s="70"/>
+      <c r="Y27" s="70"/>
+      <c r="Z27" s="70"/>
+      <c r="AA27" s="70"/>
+      <c r="AB27" s="70"/>
+      <c r="AC27" s="70"/>
+      <c r="AD27" s="70"/>
+      <c r="AE27" s="70"/>
+      <c r="AF27" s="70"/>
+      <c r="AG27" s="70"/>
+      <c r="AH27" s="66"/>
     </row>
     <row r="28" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A28" s="67" t="s">
+      <c r="A28" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="68"/>
+      <c r="B28" s="66"/>
       <c r="C28" s="3">
         <v>1</v>
       </c>
@@ -4552,7 +4332,7 @@
       </c>
     </row>
     <row r="29" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="71" t="s">
         <v>15</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -4657,7 +4437,7 @@
       </c>
     </row>
     <row r="30" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A30" s="66"/>
+      <c r="A30" s="68"/>
       <c r="B30" s="5" t="s">
         <v>7</v>
       </c>
@@ -4799,45 +4579,45 @@
       <c r="A32" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="77"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="77"/>
-      <c r="Q32" s="77"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="77"/>
-      <c r="U32" s="77"/>
-      <c r="V32" s="77"/>
-      <c r="W32" s="77"/>
-      <c r="X32" s="77"/>
-      <c r="Y32" s="77"/>
-      <c r="Z32" s="77"/>
-      <c r="AA32" s="77"/>
-      <c r="AB32" s="77"/>
-      <c r="AC32" s="77"/>
-      <c r="AD32" s="77"/>
-      <c r="AE32" s="77"/>
-      <c r="AF32" s="77"/>
-      <c r="AG32" s="77"/>
-      <c r="AH32" s="68"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
+      <c r="R32" s="70"/>
+      <c r="S32" s="70"/>
+      <c r="T32" s="70"/>
+      <c r="U32" s="70"/>
+      <c r="V32" s="70"/>
+      <c r="W32" s="70"/>
+      <c r="X32" s="70"/>
+      <c r="Y32" s="70"/>
+      <c r="Z32" s="70"/>
+      <c r="AA32" s="70"/>
+      <c r="AB32" s="70"/>
+      <c r="AC32" s="70"/>
+      <c r="AD32" s="70"/>
+      <c r="AE32" s="70"/>
+      <c r="AF32" s="70"/>
+      <c r="AG32" s="70"/>
+      <c r="AH32" s="66"/>
     </row>
     <row r="33" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A33" s="67" t="s">
+      <c r="A33" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="68"/>
+      <c r="B33" s="66"/>
       <c r="C33" s="3">
         <v>1</v>
       </c>
@@ -4936,7 +4716,7 @@
       </c>
     </row>
     <row r="34" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A34" s="69" t="s">
+      <c r="A34" s="91" t="s">
         <v>17</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -5041,7 +4821,7 @@
       </c>
     </row>
     <row r="35" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A35" s="66"/>
+      <c r="A35" s="68"/>
       <c r="B35" s="5" t="s">
         <v>7</v>
       </c>
@@ -5152,45 +4932,45 @@
       <c r="A37" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="77"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="77"/>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
-      <c r="P37" s="77"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="77"/>
-      <c r="AE37" s="77"/>
-      <c r="AF37" s="77"/>
-      <c r="AG37" s="77"/>
-      <c r="AH37" s="68"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="70"/>
+      <c r="S37" s="70"/>
+      <c r="T37" s="70"/>
+      <c r="U37" s="70"/>
+      <c r="V37" s="70"/>
+      <c r="W37" s="70"/>
+      <c r="X37" s="70"/>
+      <c r="Y37" s="70"/>
+      <c r="Z37" s="70"/>
+      <c r="AA37" s="70"/>
+      <c r="AB37" s="70"/>
+      <c r="AC37" s="70"/>
+      <c r="AD37" s="70"/>
+      <c r="AE37" s="70"/>
+      <c r="AF37" s="70"/>
+      <c r="AG37" s="70"/>
+      <c r="AH37" s="66"/>
     </row>
     <row r="38" spans="1:34" ht="32.25" customHeight="1">
       <c r="A38" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="68"/>
+      <c r="B38" s="66"/>
       <c r="C38" s="10">
         <v>1</v>
       </c>
@@ -5289,7 +5069,7 @@
       </c>
     </row>
     <row r="39" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A39" s="65" t="s">
+      <c r="A39" s="71" t="s">
         <v>19</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -5394,7 +5174,7 @@
       </c>
     </row>
     <row r="40" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A40" s="66"/>
+      <c r="A40" s="68"/>
       <c r="B40" s="5" t="s">
         <v>7</v>
       </c>
@@ -5536,45 +5316,45 @@
       <c r="A42" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="77"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="77"/>
-      <c r="M42" s="77"/>
-      <c r="N42" s="77"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="77"/>
-      <c r="Q42" s="77"/>
-      <c r="R42" s="77"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="77"/>
-      <c r="U42" s="77"/>
-      <c r="V42" s="77"/>
-      <c r="W42" s="77"/>
-      <c r="X42" s="77"/>
-      <c r="Y42" s="77"/>
-      <c r="Z42" s="77"/>
-      <c r="AA42" s="77"/>
-      <c r="AB42" s="77"/>
-      <c r="AC42" s="77"/>
-      <c r="AD42" s="77"/>
-      <c r="AE42" s="77"/>
-      <c r="AF42" s="77"/>
-      <c r="AG42" s="77"/>
-      <c r="AH42" s="68"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
+      <c r="M42" s="70"/>
+      <c r="N42" s="70"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="70"/>
+      <c r="Q42" s="70"/>
+      <c r="R42" s="70"/>
+      <c r="S42" s="70"/>
+      <c r="T42" s="70"/>
+      <c r="U42" s="70"/>
+      <c r="V42" s="70"/>
+      <c r="W42" s="70"/>
+      <c r="X42" s="70"/>
+      <c r="Y42" s="70"/>
+      <c r="Z42" s="70"/>
+      <c r="AA42" s="70"/>
+      <c r="AB42" s="70"/>
+      <c r="AC42" s="70"/>
+      <c r="AD42" s="70"/>
+      <c r="AE42" s="70"/>
+      <c r="AF42" s="70"/>
+      <c r="AG42" s="70"/>
+      <c r="AH42" s="66"/>
     </row>
     <row r="43" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="68"/>
+      <c r="B43" s="66"/>
       <c r="C43" s="3">
         <v>1</v>
       </c>
@@ -5673,7 +5453,7 @@
       </c>
     </row>
     <row r="44" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="91" t="s">
         <v>21</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -5778,7 +5558,7 @@
       </c>
     </row>
     <row r="45" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A45" s="66"/>
+      <c r="A45" s="68"/>
       <c r="B45" s="5" t="s">
         <v>7</v>
       </c>
@@ -5920,45 +5700,45 @@
       <c r="A47" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="77"/>
-      <c r="C47" s="77"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
-      <c r="J47" s="77"/>
-      <c r="K47" s="77"/>
-      <c r="L47" s="77"/>
-      <c r="M47" s="77"/>
-      <c r="N47" s="77"/>
-      <c r="O47" s="77"/>
-      <c r="P47" s="77"/>
-      <c r="Q47" s="77"/>
-      <c r="R47" s="77"/>
-      <c r="S47" s="77"/>
-      <c r="T47" s="77"/>
-      <c r="U47" s="77"/>
-      <c r="V47" s="77"/>
-      <c r="W47" s="77"/>
-      <c r="X47" s="77"/>
-      <c r="Y47" s="77"/>
-      <c r="Z47" s="77"/>
-      <c r="AA47" s="77"/>
-      <c r="AB47" s="77"/>
-      <c r="AC47" s="77"/>
-      <c r="AD47" s="77"/>
-      <c r="AE47" s="77"/>
-      <c r="AF47" s="77"/>
-      <c r="AG47" s="77"/>
-      <c r="AH47" s="68"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="70"/>
+      <c r="M47" s="70"/>
+      <c r="N47" s="70"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="70"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="70"/>
+      <c r="U47" s="70"/>
+      <c r="V47" s="70"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="70"/>
+      <c r="Z47" s="70"/>
+      <c r="AA47" s="70"/>
+      <c r="AB47" s="70"/>
+      <c r="AC47" s="70"/>
+      <c r="AD47" s="70"/>
+      <c r="AE47" s="70"/>
+      <c r="AF47" s="70"/>
+      <c r="AG47" s="70"/>
+      <c r="AH47" s="66"/>
     </row>
     <row r="48" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A48" s="67" t="s">
+      <c r="A48" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="68"/>
+      <c r="B48" s="66"/>
       <c r="C48" s="3">
         <v>1</v>
       </c>
@@ -6057,7 +5837,7 @@
       </c>
     </row>
     <row r="49" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A49" s="69" t="s">
+      <c r="A49" s="91" t="s">
         <v>21</v>
       </c>
       <c r="B49" s="5" t="s">
@@ -6162,7 +5942,7 @@
       </c>
     </row>
     <row r="50" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A50" s="66"/>
+      <c r="A50" s="68"/>
       <c r="B50" s="5" t="s">
         <v>7</v>
       </c>
@@ -6304,45 +6084,45 @@
       <c r="A52" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="77"/>
-      <c r="C52" s="77"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="77"/>
-      <c r="G52" s="77"/>
-      <c r="H52" s="77"/>
-      <c r="I52" s="77"/>
-      <c r="J52" s="77"/>
-      <c r="K52" s="77"/>
-      <c r="L52" s="77"/>
-      <c r="M52" s="77"/>
-      <c r="N52" s="77"/>
-      <c r="O52" s="77"/>
-      <c r="P52" s="77"/>
-      <c r="Q52" s="77"/>
-      <c r="R52" s="77"/>
-      <c r="S52" s="77"/>
-      <c r="T52" s="77"/>
-      <c r="U52" s="77"/>
-      <c r="V52" s="77"/>
-      <c r="W52" s="77"/>
-      <c r="X52" s="77"/>
-      <c r="Y52" s="77"/>
-      <c r="Z52" s="77"/>
-      <c r="AA52" s="77"/>
-      <c r="AB52" s="77"/>
-      <c r="AC52" s="77"/>
-      <c r="AD52" s="77"/>
-      <c r="AE52" s="77"/>
-      <c r="AF52" s="77"/>
-      <c r="AG52" s="77"/>
-      <c r="AH52" s="68"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="70"/>
+      <c r="M52" s="70"/>
+      <c r="N52" s="70"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="70"/>
+      <c r="Q52" s="70"/>
+      <c r="R52" s="70"/>
+      <c r="S52" s="70"/>
+      <c r="T52" s="70"/>
+      <c r="U52" s="70"/>
+      <c r="V52" s="70"/>
+      <c r="W52" s="70"/>
+      <c r="X52" s="70"/>
+      <c r="Y52" s="70"/>
+      <c r="Z52" s="70"/>
+      <c r="AA52" s="70"/>
+      <c r="AB52" s="70"/>
+      <c r="AC52" s="70"/>
+      <c r="AD52" s="70"/>
+      <c r="AE52" s="70"/>
+      <c r="AF52" s="70"/>
+      <c r="AG52" s="70"/>
+      <c r="AH52" s="66"/>
     </row>
     <row r="53" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A53" s="67" t="s">
+      <c r="A53" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="68"/>
+      <c r="B53" s="66"/>
       <c r="C53" s="3">
         <v>1</v>
       </c>
@@ -6441,7 +6221,7 @@
       </c>
     </row>
     <row r="54" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="91" t="s">
         <v>21</v>
       </c>
       <c r="B54" s="5" t="s">
@@ -6546,7 +6326,7 @@
       </c>
     </row>
     <row r="55" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A55" s="66"/>
+      <c r="A55" s="68"/>
       <c r="B55" s="5" t="s">
         <v>7</v>
       </c>
@@ -6685,48 +6465,48 @@
       <c r="AH56" s="2"/>
     </row>
     <row r="57" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A57" s="91" t="s">
+      <c r="A57" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="77"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="77"/>
-      <c r="K57" s="77"/>
-      <c r="L57" s="77"/>
-      <c r="M57" s="77"/>
-      <c r="N57" s="77"/>
-      <c r="O57" s="77"/>
-      <c r="P57" s="77"/>
-      <c r="Q57" s="77"/>
-      <c r="R57" s="77"/>
-      <c r="S57" s="77"/>
-      <c r="T57" s="77"/>
-      <c r="U57" s="77"/>
-      <c r="V57" s="77"/>
-      <c r="W57" s="77"/>
-      <c r="X57" s="77"/>
-      <c r="Y57" s="77"/>
-      <c r="Z57" s="77"/>
-      <c r="AA57" s="77"/>
-      <c r="AB57" s="77"/>
-      <c r="AC57" s="77"/>
-      <c r="AD57" s="77"/>
-      <c r="AE57" s="77"/>
-      <c r="AF57" s="77"/>
-      <c r="AG57" s="77"/>
-      <c r="AH57" s="68"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="70"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="70"/>
+      <c r="M57" s="70"/>
+      <c r="N57" s="70"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="70"/>
+      <c r="Q57" s="70"/>
+      <c r="R57" s="70"/>
+      <c r="S57" s="70"/>
+      <c r="T57" s="70"/>
+      <c r="U57" s="70"/>
+      <c r="V57" s="70"/>
+      <c r="W57" s="70"/>
+      <c r="X57" s="70"/>
+      <c r="Y57" s="70"/>
+      <c r="Z57" s="70"/>
+      <c r="AA57" s="70"/>
+      <c r="AB57" s="70"/>
+      <c r="AC57" s="70"/>
+      <c r="AD57" s="70"/>
+      <c r="AE57" s="70"/>
+      <c r="AF57" s="70"/>
+      <c r="AG57" s="70"/>
+      <c r="AH57" s="66"/>
     </row>
     <row r="58" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B58" s="68"/>
+      <c r="B58" s="66"/>
       <c r="C58" s="3">
         <v>1</v>
       </c>
@@ -6825,7 +6605,7 @@
       </c>
     </row>
     <row r="59" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A59" s="74" t="s">
+      <c r="A59" s="67" t="s">
         <v>25</v>
       </c>
       <c r="B59" s="5" t="s">
@@ -6930,7 +6710,7 @@
       </c>
     </row>
     <row r="60" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A60" s="66"/>
+      <c r="A60" s="68"/>
       <c r="B60" s="5" t="s">
         <v>7</v>
       </c>
@@ -7069,48 +6849,48 @@
       <c r="AH61" s="2"/>
     </row>
     <row r="62" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A62" s="91" t="s">
+      <c r="A62" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B62" s="77"/>
-      <c r="C62" s="77"/>
-      <c r="D62" s="77"/>
-      <c r="E62" s="77"/>
-      <c r="F62" s="77"/>
-      <c r="G62" s="77"/>
-      <c r="H62" s="77"/>
-      <c r="I62" s="77"/>
-      <c r="J62" s="77"/>
-      <c r="K62" s="77"/>
-      <c r="L62" s="77"/>
-      <c r="M62" s="77"/>
-      <c r="N62" s="77"/>
-      <c r="O62" s="77"/>
-      <c r="P62" s="77"/>
-      <c r="Q62" s="77"/>
-      <c r="R62" s="77"/>
-      <c r="S62" s="77"/>
-      <c r="T62" s="77"/>
-      <c r="U62" s="77"/>
-      <c r="V62" s="77"/>
-      <c r="W62" s="77"/>
-      <c r="X62" s="77"/>
-      <c r="Y62" s="77"/>
-      <c r="Z62" s="77"/>
-      <c r="AA62" s="77"/>
-      <c r="AB62" s="77"/>
-      <c r="AC62" s="77"/>
-      <c r="AD62" s="77"/>
-      <c r="AE62" s="77"/>
-      <c r="AF62" s="77"/>
-      <c r="AG62" s="77"/>
-      <c r="AH62" s="68"/>
+      <c r="B62" s="70"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="70"/>
+      <c r="I62" s="70"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="70"/>
+      <c r="M62" s="70"/>
+      <c r="N62" s="70"/>
+      <c r="O62" s="70"/>
+      <c r="P62" s="70"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="70"/>
+      <c r="T62" s="70"/>
+      <c r="U62" s="70"/>
+      <c r="V62" s="70"/>
+      <c r="W62" s="70"/>
+      <c r="X62" s="70"/>
+      <c r="Y62" s="70"/>
+      <c r="Z62" s="70"/>
+      <c r="AA62" s="70"/>
+      <c r="AB62" s="70"/>
+      <c r="AC62" s="70"/>
+      <c r="AD62" s="70"/>
+      <c r="AE62" s="70"/>
+      <c r="AF62" s="70"/>
+      <c r="AG62" s="70"/>
+      <c r="AH62" s="66"/>
     </row>
     <row r="63" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A63" s="67" t="s">
+      <c r="A63" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B63" s="68"/>
+      <c r="B63" s="66"/>
       <c r="C63" s="3">
         <v>1</v>
       </c>
@@ -7209,7 +6989,7 @@
       </c>
     </row>
     <row r="64" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A64" s="74" t="s">
+      <c r="A64" s="67" t="s">
         <v>25</v>
       </c>
       <c r="B64" s="5" t="s">
@@ -7314,7 +7094,7 @@
       </c>
     </row>
     <row r="65" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A65" s="66"/>
+      <c r="A65" s="68"/>
       <c r="B65" s="5" t="s">
         <v>7</v>
       </c>
@@ -7453,48 +7233,48 @@
       <c r="AH66" s="2"/>
     </row>
     <row r="67" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A67" s="91" t="s">
+      <c r="A67" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="B67" s="77"/>
-      <c r="C67" s="77"/>
-      <c r="D67" s="77"/>
-      <c r="E67" s="77"/>
-      <c r="F67" s="77"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="77"/>
-      <c r="I67" s="77"/>
-      <c r="J67" s="77"/>
-      <c r="K67" s="77"/>
-      <c r="L67" s="77"/>
-      <c r="M67" s="77"/>
-      <c r="N67" s="77"/>
-      <c r="O67" s="77"/>
-      <c r="P67" s="77"/>
-      <c r="Q67" s="77"/>
-      <c r="R67" s="77"/>
-      <c r="S67" s="77"/>
-      <c r="T67" s="77"/>
-      <c r="U67" s="77"/>
-      <c r="V67" s="77"/>
-      <c r="W67" s="77"/>
-      <c r="X67" s="77"/>
-      <c r="Y67" s="77"/>
-      <c r="Z67" s="77"/>
-      <c r="AA67" s="77"/>
-      <c r="AB67" s="77"/>
-      <c r="AC67" s="77"/>
-      <c r="AD67" s="77"/>
-      <c r="AE67" s="77"/>
-      <c r="AF67" s="77"/>
-      <c r="AG67" s="77"/>
-      <c r="AH67" s="68"/>
+      <c r="B67" s="70"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
+      <c r="M67" s="70"/>
+      <c r="N67" s="70"/>
+      <c r="O67" s="70"/>
+      <c r="P67" s="70"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="70"/>
+      <c r="T67" s="70"/>
+      <c r="U67" s="70"/>
+      <c r="V67" s="70"/>
+      <c r="W67" s="70"/>
+      <c r="X67" s="70"/>
+      <c r="Y67" s="70"/>
+      <c r="Z67" s="70"/>
+      <c r="AA67" s="70"/>
+      <c r="AB67" s="70"/>
+      <c r="AC67" s="70"/>
+      <c r="AD67" s="70"/>
+      <c r="AE67" s="70"/>
+      <c r="AF67" s="70"/>
+      <c r="AG67" s="70"/>
+      <c r="AH67" s="66"/>
     </row>
     <row r="68" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="68"/>
+      <c r="B68" s="66"/>
       <c r="C68" s="3">
         <v>1</v>
       </c>
@@ -7593,7 +7373,7 @@
       </c>
     </row>
     <row r="69" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A69" s="74" t="s">
+      <c r="A69" s="67" t="s">
         <v>25</v>
       </c>
       <c r="B69" s="5" t="s">
@@ -7698,7 +7478,7 @@
       </c>
     </row>
     <row r="70" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A70" s="66"/>
+      <c r="A70" s="68"/>
       <c r="B70" s="5" t="s">
         <v>7</v>
       </c>
@@ -7837,48 +7617,48 @@
       <c r="AH71" s="2"/>
     </row>
     <row r="72" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A72" s="91" t="s">
+      <c r="A72" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="B72" s="77"/>
-      <c r="C72" s="77"/>
-      <c r="D72" s="77"/>
-      <c r="E72" s="77"/>
-      <c r="F72" s="77"/>
-      <c r="G72" s="77"/>
-      <c r="H72" s="77"/>
-      <c r="I72" s="77"/>
-      <c r="J72" s="77"/>
-      <c r="K72" s="77"/>
-      <c r="L72" s="77"/>
-      <c r="M72" s="77"/>
-      <c r="N72" s="77"/>
-      <c r="O72" s="77"/>
-      <c r="P72" s="77"/>
-      <c r="Q72" s="77"/>
-      <c r="R72" s="77"/>
-      <c r="S72" s="77"/>
-      <c r="T72" s="77"/>
-      <c r="U72" s="77"/>
-      <c r="V72" s="77"/>
-      <c r="W72" s="77"/>
-      <c r="X72" s="77"/>
-      <c r="Y72" s="77"/>
-      <c r="Z72" s="77"/>
-      <c r="AA72" s="77"/>
-      <c r="AB72" s="77"/>
-      <c r="AC72" s="77"/>
-      <c r="AD72" s="77"/>
-      <c r="AE72" s="77"/>
-      <c r="AF72" s="77"/>
-      <c r="AG72" s="77"/>
-      <c r="AH72" s="68"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="70"/>
+      <c r="E72" s="70"/>
+      <c r="F72" s="70"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="70"/>
+      <c r="I72" s="70"/>
+      <c r="J72" s="70"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="70"/>
+      <c r="M72" s="70"/>
+      <c r="N72" s="70"/>
+      <c r="O72" s="70"/>
+      <c r="P72" s="70"/>
+      <c r="Q72" s="70"/>
+      <c r="R72" s="70"/>
+      <c r="S72" s="70"/>
+      <c r="T72" s="70"/>
+      <c r="U72" s="70"/>
+      <c r="V72" s="70"/>
+      <c r="W72" s="70"/>
+      <c r="X72" s="70"/>
+      <c r="Y72" s="70"/>
+      <c r="Z72" s="70"/>
+      <c r="AA72" s="70"/>
+      <c r="AB72" s="70"/>
+      <c r="AC72" s="70"/>
+      <c r="AD72" s="70"/>
+      <c r="AE72" s="70"/>
+      <c r="AF72" s="70"/>
+      <c r="AG72" s="70"/>
+      <c r="AH72" s="66"/>
     </row>
     <row r="73" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A73" s="67" t="s">
+      <c r="A73" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B73" s="68"/>
+      <c r="B73" s="66"/>
       <c r="C73" s="3">
         <v>1</v>
       </c>
@@ -8223,48 +8003,48 @@
       <c r="AH76" s="2"/>
     </row>
     <row r="77" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A77" s="91" t="s">
+      <c r="A77" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="B77" s="77"/>
-      <c r="C77" s="77"/>
-      <c r="D77" s="77"/>
-      <c r="E77" s="77"/>
-      <c r="F77" s="77"/>
-      <c r="G77" s="77"/>
-      <c r="H77" s="77"/>
-      <c r="I77" s="77"/>
-      <c r="J77" s="77"/>
-      <c r="K77" s="77"/>
-      <c r="L77" s="77"/>
-      <c r="M77" s="77"/>
-      <c r="N77" s="77"/>
-      <c r="O77" s="77"/>
-      <c r="P77" s="77"/>
-      <c r="Q77" s="77"/>
-      <c r="R77" s="77"/>
-      <c r="S77" s="77"/>
-      <c r="T77" s="77"/>
-      <c r="U77" s="77"/>
-      <c r="V77" s="77"/>
-      <c r="W77" s="77"/>
-      <c r="X77" s="77"/>
-      <c r="Y77" s="77"/>
-      <c r="Z77" s="77"/>
-      <c r="AA77" s="77"/>
-      <c r="AB77" s="77"/>
-      <c r="AC77" s="77"/>
-      <c r="AD77" s="77"/>
-      <c r="AE77" s="77"/>
-      <c r="AF77" s="77"/>
-      <c r="AG77" s="77"/>
-      <c r="AH77" s="68"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="70"/>
+      <c r="H77" s="70"/>
+      <c r="I77" s="70"/>
+      <c r="J77" s="70"/>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
+      <c r="M77" s="70"/>
+      <c r="N77" s="70"/>
+      <c r="O77" s="70"/>
+      <c r="P77" s="70"/>
+      <c r="Q77" s="70"/>
+      <c r="R77" s="70"/>
+      <c r="S77" s="70"/>
+      <c r="T77" s="70"/>
+      <c r="U77" s="70"/>
+      <c r="V77" s="70"/>
+      <c r="W77" s="70"/>
+      <c r="X77" s="70"/>
+      <c r="Y77" s="70"/>
+      <c r="Z77" s="70"/>
+      <c r="AA77" s="70"/>
+      <c r="AB77" s="70"/>
+      <c r="AC77" s="70"/>
+      <c r="AD77" s="70"/>
+      <c r="AE77" s="70"/>
+      <c r="AF77" s="70"/>
+      <c r="AG77" s="70"/>
+      <c r="AH77" s="66"/>
     </row>
     <row r="78" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A78" s="67" t="s">
+      <c r="A78" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B78" s="68"/>
+      <c r="B78" s="66"/>
       <c r="C78" s="3">
         <v>1</v>
       </c>
@@ -8363,7 +8143,7 @@
       </c>
     </row>
     <row r="79" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A79" s="74" t="s">
+      <c r="A79" s="67" t="s">
         <v>25</v>
       </c>
       <c r="B79" s="5" t="s">
@@ -8468,7 +8248,7 @@
       </c>
     </row>
     <row r="80" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A80" s="66"/>
+      <c r="A80" s="68"/>
       <c r="B80" s="5" t="s">
         <v>7</v>
       </c>
@@ -8610,45 +8390,45 @@
       <c r="A82" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="77"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="77"/>
-      <c r="G82" s="77"/>
-      <c r="H82" s="77"/>
-      <c r="I82" s="77"/>
-      <c r="J82" s="77"/>
-      <c r="K82" s="77"/>
-      <c r="L82" s="77"/>
-      <c r="M82" s="77"/>
-      <c r="N82" s="77"/>
-      <c r="O82" s="77"/>
-      <c r="P82" s="77"/>
-      <c r="Q82" s="77"/>
-      <c r="R82" s="77"/>
-      <c r="S82" s="77"/>
-      <c r="T82" s="77"/>
-      <c r="U82" s="77"/>
-      <c r="V82" s="77"/>
-      <c r="W82" s="77"/>
-      <c r="X82" s="77"/>
-      <c r="Y82" s="77"/>
-      <c r="Z82" s="77"/>
-      <c r="AA82" s="77"/>
-      <c r="AB82" s="77"/>
-      <c r="AC82" s="77"/>
-      <c r="AD82" s="77"/>
-      <c r="AE82" s="77"/>
-      <c r="AF82" s="77"/>
-      <c r="AG82" s="77"/>
-      <c r="AH82" s="68"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="70"/>
+      <c r="M82" s="70"/>
+      <c r="N82" s="70"/>
+      <c r="O82" s="70"/>
+      <c r="P82" s="70"/>
+      <c r="Q82" s="70"/>
+      <c r="R82" s="70"/>
+      <c r="S82" s="70"/>
+      <c r="T82" s="70"/>
+      <c r="U82" s="70"/>
+      <c r="V82" s="70"/>
+      <c r="W82" s="70"/>
+      <c r="X82" s="70"/>
+      <c r="Y82" s="70"/>
+      <c r="Z82" s="70"/>
+      <c r="AA82" s="70"/>
+      <c r="AB82" s="70"/>
+      <c r="AC82" s="70"/>
+      <c r="AD82" s="70"/>
+      <c r="AE82" s="70"/>
+      <c r="AF82" s="70"/>
+      <c r="AG82" s="70"/>
+      <c r="AH82" s="66"/>
     </row>
     <row r="83" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A83" s="67" t="s">
+      <c r="A83" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B83" s="68"/>
+      <c r="B83" s="66"/>
       <c r="C83" s="3">
         <v>1</v>
       </c>
@@ -8747,7 +8527,7 @@
       </c>
     </row>
     <row r="84" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A84" s="65" t="s">
+      <c r="A84" s="71" t="s">
         <v>32</v>
       </c>
       <c r="B84" s="5" t="s">
@@ -8852,7 +8632,7 @@
       </c>
     </row>
     <row r="85" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A85" s="66"/>
+      <c r="A85" s="68"/>
       <c r="B85" s="5" t="s">
         <v>7</v>
       </c>
@@ -8994,45 +8774,45 @@
       <c r="A87" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="B87" s="77"/>
-      <c r="C87" s="77"/>
-      <c r="D87" s="77"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="77"/>
-      <c r="I87" s="77"/>
-      <c r="J87" s="77"/>
-      <c r="K87" s="77"/>
-      <c r="L87" s="77"/>
-      <c r="M87" s="77"/>
-      <c r="N87" s="77"/>
-      <c r="O87" s="77"/>
-      <c r="P87" s="77"/>
-      <c r="Q87" s="77"/>
-      <c r="R87" s="77"/>
-      <c r="S87" s="77"/>
-      <c r="T87" s="77"/>
-      <c r="U87" s="77"/>
-      <c r="V87" s="77"/>
-      <c r="W87" s="77"/>
-      <c r="X87" s="77"/>
-      <c r="Y87" s="77"/>
-      <c r="Z87" s="77"/>
-      <c r="AA87" s="77"/>
-      <c r="AB87" s="77"/>
-      <c r="AC87" s="77"/>
-      <c r="AD87" s="77"/>
-      <c r="AE87" s="77"/>
-      <c r="AF87" s="77"/>
-      <c r="AG87" s="77"/>
-      <c r="AH87" s="68"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="70"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
+      <c r="N87" s="70"/>
+      <c r="O87" s="70"/>
+      <c r="P87" s="70"/>
+      <c r="Q87" s="70"/>
+      <c r="R87" s="70"/>
+      <c r="S87" s="70"/>
+      <c r="T87" s="70"/>
+      <c r="U87" s="70"/>
+      <c r="V87" s="70"/>
+      <c r="W87" s="70"/>
+      <c r="X87" s="70"/>
+      <c r="Y87" s="70"/>
+      <c r="Z87" s="70"/>
+      <c r="AA87" s="70"/>
+      <c r="AB87" s="70"/>
+      <c r="AC87" s="70"/>
+      <c r="AD87" s="70"/>
+      <c r="AE87" s="70"/>
+      <c r="AF87" s="70"/>
+      <c r="AG87" s="70"/>
+      <c r="AH87" s="66"/>
     </row>
     <row r="88" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A88" s="67" t="s">
+      <c r="A88" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B88" s="68"/>
+      <c r="B88" s="66"/>
       <c r="C88" s="3">
         <v>1</v>
       </c>
@@ -9131,7 +8911,7 @@
       </c>
     </row>
     <row r="89" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A89" s="65" t="s">
+      <c r="A89" s="71" t="s">
         <v>32</v>
       </c>
       <c r="B89" s="5" t="s">
@@ -9165,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="7">
         <v>0</v>
@@ -9183,10 +8963,10 @@
         <v>0</v>
       </c>
       <c r="R89" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S89" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" s="7">
         <v>0</v>
@@ -9210,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="AA89" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB89" s="7">
         <v>0</v>
@@ -9232,11 +9012,11 @@
       </c>
       <c r="AH89" s="8">
         <f t="shared" ref="AH89:AH90" si="15">SUM(C89:AG89)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A90" s="66"/>
+      <c r="A90" s="68"/>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
@@ -9265,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="7">
         <v>0</v>
@@ -9277,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P90" s="7">
         <v>0</v>
@@ -9310,7 +9090,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA90" s="7">
         <v>0</v>
@@ -9335,7 +9115,7 @@
       </c>
       <c r="AH90" s="8">
         <f t="shared" si="15"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:34" ht="32.25" customHeight="1">
@@ -9378,45 +9158,45 @@
       <c r="A92" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="B92" s="77"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
-      <c r="E92" s="77"/>
-      <c r="F92" s="77"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="77"/>
-      <c r="I92" s="77"/>
-      <c r="J92" s="77"/>
-      <c r="K92" s="77"/>
-      <c r="L92" s="77"/>
-      <c r="M92" s="77"/>
-      <c r="N92" s="77"/>
-      <c r="O92" s="77"/>
-      <c r="P92" s="77"/>
-      <c r="Q92" s="77"/>
-      <c r="R92" s="77"/>
-      <c r="S92" s="77"/>
-      <c r="T92" s="77"/>
-      <c r="U92" s="77"/>
-      <c r="V92" s="77"/>
-      <c r="W92" s="77"/>
-      <c r="X92" s="77"/>
-      <c r="Y92" s="77"/>
-      <c r="Z92" s="77"/>
-      <c r="AA92" s="77"/>
-      <c r="AB92" s="77"/>
-      <c r="AC92" s="77"/>
-      <c r="AD92" s="77"/>
-      <c r="AE92" s="77"/>
-      <c r="AF92" s="77"/>
-      <c r="AG92" s="77"/>
-      <c r="AH92" s="68"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="70"/>
+      <c r="E92" s="70"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="70"/>
+      <c r="H92" s="70"/>
+      <c r="I92" s="70"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="70"/>
+      <c r="M92" s="70"/>
+      <c r="N92" s="70"/>
+      <c r="O92" s="70"/>
+      <c r="P92" s="70"/>
+      <c r="Q92" s="70"/>
+      <c r="R92" s="70"/>
+      <c r="S92" s="70"/>
+      <c r="T92" s="70"/>
+      <c r="U92" s="70"/>
+      <c r="V92" s="70"/>
+      <c r="W92" s="70"/>
+      <c r="X92" s="70"/>
+      <c r="Y92" s="70"/>
+      <c r="Z92" s="70"/>
+      <c r="AA92" s="70"/>
+      <c r="AB92" s="70"/>
+      <c r="AC92" s="70"/>
+      <c r="AD92" s="70"/>
+      <c r="AE92" s="70"/>
+      <c r="AF92" s="70"/>
+      <c r="AG92" s="70"/>
+      <c r="AH92" s="66"/>
     </row>
     <row r="93" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A93" s="67" t="s">
+      <c r="A93" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B93" s="68"/>
+      <c r="B93" s="66"/>
       <c r="C93" s="3">
         <v>1</v>
       </c>
@@ -9515,7 +9295,7 @@
       </c>
     </row>
     <row r="94" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A94" s="65" t="s">
+      <c r="A94" s="71" t="s">
         <v>32</v>
       </c>
       <c r="B94" s="5" t="s">
@@ -9620,7 +9400,7 @@
       </c>
     </row>
     <row r="95" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A95" s="66"/>
+      <c r="A95" s="68"/>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
@@ -9795,48 +9575,48 @@
       <c r="AH97" s="2"/>
     </row>
     <row r="98" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A98" s="78" t="s">
+      <c r="A98" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="77"/>
-      <c r="D98" s="77"/>
-      <c r="E98" s="77"/>
-      <c r="F98" s="77"/>
-      <c r="G98" s="77"/>
-      <c r="H98" s="77"/>
-      <c r="I98" s="77"/>
-      <c r="J98" s="77"/>
-      <c r="K98" s="77"/>
-      <c r="L98" s="77"/>
-      <c r="M98" s="77"/>
-      <c r="N98" s="77"/>
-      <c r="O98" s="77"/>
-      <c r="P98" s="77"/>
-      <c r="Q98" s="77"/>
-      <c r="R98" s="77"/>
-      <c r="S98" s="77"/>
-      <c r="T98" s="77"/>
-      <c r="U98" s="77"/>
-      <c r="V98" s="77"/>
-      <c r="W98" s="77"/>
-      <c r="X98" s="77"/>
-      <c r="Y98" s="77"/>
-      <c r="Z98" s="77"/>
-      <c r="AA98" s="77"/>
-      <c r="AB98" s="77"/>
-      <c r="AC98" s="77"/>
-      <c r="AD98" s="77"/>
-      <c r="AE98" s="77"/>
-      <c r="AF98" s="77"/>
-      <c r="AG98" s="77"/>
-      <c r="AH98" s="68"/>
+      <c r="B98" s="70"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="70"/>
+      <c r="F98" s="70"/>
+      <c r="G98" s="70"/>
+      <c r="H98" s="70"/>
+      <c r="I98" s="70"/>
+      <c r="J98" s="70"/>
+      <c r="K98" s="70"/>
+      <c r="L98" s="70"/>
+      <c r="M98" s="70"/>
+      <c r="N98" s="70"/>
+      <c r="O98" s="70"/>
+      <c r="P98" s="70"/>
+      <c r="Q98" s="70"/>
+      <c r="R98" s="70"/>
+      <c r="S98" s="70"/>
+      <c r="T98" s="70"/>
+      <c r="U98" s="70"/>
+      <c r="V98" s="70"/>
+      <c r="W98" s="70"/>
+      <c r="X98" s="70"/>
+      <c r="Y98" s="70"/>
+      <c r="Z98" s="70"/>
+      <c r="AA98" s="70"/>
+      <c r="AB98" s="70"/>
+      <c r="AC98" s="70"/>
+      <c r="AD98" s="70"/>
+      <c r="AE98" s="70"/>
+      <c r="AF98" s="70"/>
+      <c r="AG98" s="70"/>
+      <c r="AH98" s="66"/>
     </row>
     <row r="99" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B99" s="68"/>
+      <c r="B99" s="66"/>
       <c r="C99" s="20">
         <v>1</v>
       </c>
@@ -9935,7 +9715,7 @@
       </c>
     </row>
     <row r="100" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A100" s="70" t="s">
+      <c r="A100" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B100" s="5" t="s">
@@ -10040,7 +9820,7 @@
       </c>
     </row>
     <row r="101" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A101" s="66"/>
+      <c r="A101" s="68"/>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
@@ -10179,48 +9959,48 @@
       <c r="AH102" s="22"/>
     </row>
     <row r="103" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A103" s="79" t="s">
+      <c r="A103" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
-      <c r="H103" s="77"/>
-      <c r="I103" s="77"/>
-      <c r="J103" s="77"/>
-      <c r="K103" s="77"/>
-      <c r="L103" s="77"/>
-      <c r="M103" s="77"/>
-      <c r="N103" s="77"/>
-      <c r="O103" s="77"/>
-      <c r="P103" s="77"/>
-      <c r="Q103" s="77"/>
-      <c r="R103" s="77"/>
-      <c r="S103" s="77"/>
-      <c r="T103" s="77"/>
-      <c r="U103" s="77"/>
-      <c r="V103" s="77"/>
-      <c r="W103" s="77"/>
-      <c r="X103" s="77"/>
-      <c r="Y103" s="77"/>
-      <c r="Z103" s="77"/>
-      <c r="AA103" s="77"/>
-      <c r="AB103" s="77"/>
-      <c r="AC103" s="77"/>
-      <c r="AD103" s="77"/>
-      <c r="AE103" s="77"/>
-      <c r="AF103" s="77"/>
-      <c r="AG103" s="77"/>
-      <c r="AH103" s="68"/>
+      <c r="B103" s="70"/>
+      <c r="C103" s="70"/>
+      <c r="D103" s="70"/>
+      <c r="E103" s="70"/>
+      <c r="F103" s="70"/>
+      <c r="G103" s="70"/>
+      <c r="H103" s="70"/>
+      <c r="I103" s="70"/>
+      <c r="J103" s="70"/>
+      <c r="K103" s="70"/>
+      <c r="L103" s="70"/>
+      <c r="M103" s="70"/>
+      <c r="N103" s="70"/>
+      <c r="O103" s="70"/>
+      <c r="P103" s="70"/>
+      <c r="Q103" s="70"/>
+      <c r="R103" s="70"/>
+      <c r="S103" s="70"/>
+      <c r="T103" s="70"/>
+      <c r="U103" s="70"/>
+      <c r="V103" s="70"/>
+      <c r="W103" s="70"/>
+      <c r="X103" s="70"/>
+      <c r="Y103" s="70"/>
+      <c r="Z103" s="70"/>
+      <c r="AA103" s="70"/>
+      <c r="AB103" s="70"/>
+      <c r="AC103" s="70"/>
+      <c r="AD103" s="70"/>
+      <c r="AE103" s="70"/>
+      <c r="AF103" s="70"/>
+      <c r="AG103" s="70"/>
+      <c r="AH103" s="66"/>
     </row>
     <row r="104" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A104" s="67" t="s">
+      <c r="A104" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B104" s="68"/>
+      <c r="B104" s="66"/>
       <c r="C104" s="20">
         <v>1</v>
       </c>
@@ -10319,7 +10099,7 @@
       </c>
     </row>
     <row r="105" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A105" s="70" t="s">
+      <c r="A105" s="82" t="s">
         <v>36</v>
       </c>
       <c r="B105" s="5" t="s">
@@ -10424,7 +10204,7 @@
       </c>
     </row>
     <row r="106" spans="1:34" ht="32.25" customHeight="1">
-      <c r="A106" s="66"/>
+      <c r="A106" s="68"/>
       <c r="B106" s="5" t="s">
         <v>7</v>
       </c>
@@ -10790,15 +10570,15 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
-      <c r="J114" s="80" t="s">
+      <c r="J114" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="K114" s="72"/>
-      <c r="L114" s="72"/>
-      <c r="M114" s="72"/>
-      <c r="N114" s="72"/>
-      <c r="O114" s="72"/>
-      <c r="P114" s="72"/>
+      <c r="K114" s="73"/>
+      <c r="L114" s="73"/>
+      <c r="M114" s="73"/>
+      <c r="N114" s="73"/>
+      <c r="O114" s="73"/>
+      <c r="P114" s="73"/>
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
@@ -10810,14 +10590,14 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
-      <c r="AB114" s="81" t="s">
+      <c r="AB114" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="AC114" s="72"/>
-      <c r="AD114" s="72"/>
-      <c r="AE114" s="72"/>
-      <c r="AF114" s="72"/>
-      <c r="AG114" s="72"/>
+      <c r="AC114" s="73"/>
+      <c r="AD114" s="73"/>
+      <c r="AE114" s="73"/>
+      <c r="AF114" s="73"/>
+      <c r="AG114" s="73"/>
       <c r="AH114" s="24"/>
     </row>
     <row r="115" spans="1:34" ht="15.75" customHeight="1">
@@ -10893,10 +10673,10 @@
       <c r="AH116" s="23"/>
     </row>
     <row r="117" spans="1:34" ht="15.75" customHeight="1">
-      <c r="A117" s="71" t="s">
+      <c r="A117" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="B117" s="72"/>
+      <c r="B117" s="73"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
@@ -10904,16 +10684,16 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-      <c r="J117" s="71" t="s">
+      <c r="J117" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="K117" s="72"/>
-      <c r="L117" s="72"/>
-      <c r="M117" s="72"/>
-      <c r="N117" s="72"/>
-      <c r="O117" s="72"/>
-      <c r="P117" s="72"/>
-      <c r="Q117" s="72"/>
+      <c r="K117" s="73"/>
+      <c r="L117" s="73"/>
+      <c r="M117" s="73"/>
+      <c r="N117" s="73"/>
+      <c r="O117" s="73"/>
+      <c r="P117" s="73"/>
+      <c r="Q117" s="73"/>
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
@@ -10924,21 +10704,21 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
-      <c r="AB117" s="82" t="s">
+      <c r="AB117" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="AC117" s="72"/>
-      <c r="AD117" s="72"/>
-      <c r="AE117" s="72"/>
-      <c r="AF117" s="72"/>
-      <c r="AG117" s="72"/>
-      <c r="AH117" s="72"/>
+      <c r="AC117" s="73"/>
+      <c r="AD117" s="73"/>
+      <c r="AE117" s="73"/>
+      <c r="AF117" s="73"/>
+      <c r="AG117" s="73"/>
+      <c r="AH117" s="73"/>
     </row>
     <row r="118" spans="1:34" ht="15.75" customHeight="1">
-      <c r="A118" s="73" t="s">
+      <c r="A118" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="B118" s="72"/>
+      <c r="B118" s="73"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
@@ -10946,15 +10726,15 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
-      <c r="J118" s="73" t="s">
+      <c r="J118" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="K118" s="72"/>
-      <c r="L118" s="72"/>
-      <c r="M118" s="72"/>
-      <c r="N118" s="72"/>
-      <c r="O118" s="72"/>
-      <c r="P118" s="72"/>
+      <c r="K118" s="73"/>
+      <c r="L118" s="73"/>
+      <c r="M118" s="73"/>
+      <c r="N118" s="73"/>
+      <c r="O118" s="73"/>
+      <c r="P118" s="73"/>
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
@@ -10969,16 +10749,16 @@
       <c r="AB118" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="AC118" s="72"/>
-      <c r="AD118" s="72"/>
-      <c r="AE118" s="72"/>
-      <c r="AF118" s="72"/>
-      <c r="AG118" s="72"/>
+      <c r="AC118" s="73"/>
+      <c r="AD118" s="73"/>
+      <c r="AE118" s="73"/>
+      <c r="AF118" s="73"/>
+      <c r="AG118" s="73"/>
       <c r="AH118" s="28"/>
     </row>
     <row r="119" spans="1:34" ht="15.75" customHeight="1">
-      <c r="A119" s="72"/>
-      <c r="B119" s="72"/>
+      <c r="A119" s="73"/>
+      <c r="B119" s="73"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
@@ -10986,13 +10766,13 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
-      <c r="J119" s="72"/>
-      <c r="K119" s="72"/>
-      <c r="L119" s="72"/>
-      <c r="M119" s="72"/>
-      <c r="N119" s="72"/>
-      <c r="O119" s="72"/>
-      <c r="P119" s="72"/>
+      <c r="J119" s="73"/>
+      <c r="K119" s="73"/>
+      <c r="L119" s="73"/>
+      <c r="M119" s="73"/>
+      <c r="N119" s="73"/>
+      <c r="O119" s="73"/>
+      <c r="P119" s="73"/>
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
@@ -11004,12 +10784,12 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
-      <c r="AB119" s="72"/>
-      <c r="AC119" s="72"/>
-      <c r="AD119" s="72"/>
-      <c r="AE119" s="72"/>
-      <c r="AF119" s="72"/>
-      <c r="AG119" s="72"/>
+      <c r="AB119" s="73"/>
+      <c r="AC119" s="73"/>
+      <c r="AD119" s="73"/>
+      <c r="AE119" s="73"/>
+      <c r="AF119" s="73"/>
+      <c r="AG119" s="73"/>
       <c r="AH119" s="28"/>
     </row>
     <row r="120" spans="1:34" ht="15.75" customHeight="1">
@@ -21542,32 +21322,42 @@
     <row r="953" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A82:AH82"/>
-    <mergeCell ref="A52:AH52"/>
-    <mergeCell ref="A57:AH57"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A42:AH42"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:A50"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A32:AH32"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A37:AH37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A42:AH42"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A82:AH82"/>
+    <mergeCell ref="A52:AH52"/>
+    <mergeCell ref="A57:AH57"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A10:AG10"/>
+    <mergeCell ref="A11:AH11"/>
+    <mergeCell ref="A12:AH12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A17:AH17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A22:AH22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A27:AH27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A47:AH47"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A17:AH17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A22:AH22"/>
-    <mergeCell ref="A1:AH8"/>
-    <mergeCell ref="A10:AG10"/>
-    <mergeCell ref="A11:AH11"/>
-    <mergeCell ref="A12:AH12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="J117:Q117"/>
     <mergeCell ref="J118:P119"/>
     <mergeCell ref="AB118:AG119"/>
@@ -21581,17 +21371,8 @@
     <mergeCell ref="A105:A106"/>
     <mergeCell ref="A117:B117"/>
     <mergeCell ref="A118:B119"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A54:A55"/>
     <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A100:A101"/>
     <mergeCell ref="A104:B104"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:A60"/>
@@ -21604,11 +21385,10 @@
     <mergeCell ref="A72:AH72"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A77:AH77"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A89:A90"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.24" bottom="0.24" header="0" footer="0"/>
   <pageSetup paperSize="14" fitToHeight="0" orientation="landscape"/>
@@ -21637,280 +21417,280 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="15.75">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
-      <c r="AM1" s="72"/>
-      <c r="AN1" s="72"/>
-      <c r="AO1" s="72"/>
-      <c r="AP1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
+      <c r="AH1" s="73"/>
+      <c r="AI1" s="73"/>
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="73"/>
+      <c r="AL1" s="73"/>
+      <c r="AM1" s="73"/>
+      <c r="AN1" s="73"/>
+      <c r="AO1" s="73"/>
+      <c r="AP1" s="73"/>
     </row>
     <row r="2" spans="1:42" ht="20.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
-      <c r="Y2" s="72"/>
-      <c r="Z2" s="72"/>
-      <c r="AA2" s="72"/>
-      <c r="AB2" s="72"/>
-      <c r="AC2" s="72"/>
-      <c r="AD2" s="72"/>
-      <c r="AE2" s="72"/>
-      <c r="AF2" s="72"/>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
-      <c r="AI2" s="72"/>
-      <c r="AJ2" s="72"/>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="72"/>
-      <c r="AM2" s="72"/>
-      <c r="AN2" s="72"/>
-      <c r="AO2" s="72"/>
-      <c r="AP2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
+      <c r="W2" s="73"/>
+      <c r="X2" s="73"/>
+      <c r="Y2" s="73"/>
+      <c r="Z2" s="73"/>
+      <c r="AA2" s="73"/>
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="73"/>
+      <c r="AD2" s="73"/>
+      <c r="AE2" s="73"/>
+      <c r="AF2" s="73"/>
+      <c r="AG2" s="73"/>
+      <c r="AH2" s="73"/>
+      <c r="AI2" s="73"/>
+      <c r="AJ2" s="73"/>
+      <c r="AK2" s="73"/>
+      <c r="AL2" s="73"/>
+      <c r="AM2" s="73"/>
+      <c r="AN2" s="73"/>
+      <c r="AO2" s="73"/>
+      <c r="AP2" s="73"/>
     </row>
     <row r="3" spans="1:42" ht="15.75">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="72"/>
-      <c r="AK3" s="72"/>
-      <c r="AL3" s="72"/>
-      <c r="AM3" s="72"/>
-      <c r="AN3" s="72"/>
-      <c r="AO3" s="72"/>
-      <c r="AP3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="73"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="73"/>
+      <c r="AD3" s="73"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73"/>
+      <c r="AH3" s="73"/>
+      <c r="AI3" s="73"/>
+      <c r="AJ3" s="73"/>
+      <c r="AK3" s="73"/>
+      <c r="AL3" s="73"/>
+      <c r="AM3" s="73"/>
+      <c r="AN3" s="73"/>
+      <c r="AO3" s="73"/>
+      <c r="AP3" s="73"/>
     </row>
     <row r="4" spans="1:42" ht="15.75">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
-      <c r="U4" s="72"/>
-      <c r="V4" s="72"/>
-      <c r="W4" s="72"/>
-      <c r="X4" s="72"/>
-      <c r="Y4" s="72"/>
-      <c r="Z4" s="72"/>
-      <c r="AA4" s="72"/>
-      <c r="AB4" s="72"/>
-      <c r="AC4" s="72"/>
-      <c r="AD4" s="72"/>
-      <c r="AE4" s="72"/>
-      <c r="AF4" s="72"/>
-      <c r="AG4" s="72"/>
-      <c r="AH4" s="72"/>
-      <c r="AI4" s="72"/>
-      <c r="AJ4" s="72"/>
-      <c r="AK4" s="72"/>
-      <c r="AL4" s="72"/>
-      <c r="AM4" s="72"/>
-      <c r="AN4" s="72"/>
-      <c r="AO4" s="72"/>
-      <c r="AP4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
+      <c r="Y4" s="73"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="73"/>
+      <c r="AC4" s="73"/>
+      <c r="AD4" s="73"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
+      <c r="AI4" s="73"/>
+      <c r="AJ4" s="73"/>
+      <c r="AK4" s="73"/>
+      <c r="AL4" s="73"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="73"/>
+      <c r="AO4" s="73"/>
+      <c r="AP4" s="73"/>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="72"/>
-      <c r="U5" s="72"/>
-      <c r="V5" s="72"/>
-      <c r="W5" s="72"/>
-      <c r="X5" s="72"/>
-      <c r="Y5" s="72"/>
-      <c r="Z5" s="72"/>
-      <c r="AA5" s="72"/>
-      <c r="AB5" s="72"/>
-      <c r="AC5" s="72"/>
-      <c r="AD5" s="72"/>
-      <c r="AE5" s="72"/>
-      <c r="AF5" s="72"/>
-      <c r="AG5" s="72"/>
-      <c r="AH5" s="72"/>
-      <c r="AI5" s="72"/>
-      <c r="AJ5" s="72"/>
-      <c r="AK5" s="72"/>
-      <c r="AL5" s="72"/>
-      <c r="AM5" s="72"/>
-      <c r="AN5" s="72"/>
-      <c r="AO5" s="72"/>
-      <c r="AP5" s="72"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="73"/>
+      <c r="V5" s="73"/>
+      <c r="W5" s="73"/>
+      <c r="X5" s="73"/>
+      <c r="Y5" s="73"/>
+      <c r="Z5" s="73"/>
+      <c r="AA5" s="73"/>
+      <c r="AB5" s="73"/>
+      <c r="AC5" s="73"/>
+      <c r="AD5" s="73"/>
+      <c r="AE5" s="73"/>
+      <c r="AF5" s="73"/>
+      <c r="AG5" s="73"/>
+      <c r="AH5" s="73"/>
+      <c r="AI5" s="73"/>
+      <c r="AJ5" s="73"/>
+      <c r="AK5" s="73"/>
+      <c r="AL5" s="73"/>
+      <c r="AM5" s="73"/>
+      <c r="AN5" s="73"/>
+      <c r="AO5" s="73"/>
+      <c r="AP5" s="73"/>
     </row>
     <row r="6" spans="1:42">
       <c r="A6" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="72"/>
-      <c r="V6" s="72"/>
-      <c r="W6" s="72"/>
-      <c r="X6" s="72"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="72"/>
-      <c r="AA6" s="72"/>
-      <c r="AB6" s="72"/>
-      <c r="AC6" s="72"/>
-      <c r="AD6" s="72"/>
-      <c r="AE6" s="72"/>
-      <c r="AF6" s="72"/>
-      <c r="AG6" s="72"/>
-      <c r="AH6" s="72"/>
-      <c r="AI6" s="72"/>
-      <c r="AJ6" s="72"/>
-      <c r="AK6" s="72"/>
-      <c r="AL6" s="72"/>
-      <c r="AM6" s="72"/>
-      <c r="AN6" s="72"/>
-      <c r="AO6" s="72"/>
-      <c r="AP6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="73"/>
+      <c r="Z6" s="73"/>
+      <c r="AA6" s="73"/>
+      <c r="AB6" s="73"/>
+      <c r="AC6" s="73"/>
+      <c r="AD6" s="73"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="73"/>
+      <c r="AG6" s="73"/>
+      <c r="AH6" s="73"/>
+      <c r="AI6" s="73"/>
+      <c r="AJ6" s="73"/>
+      <c r="AK6" s="73"/>
+      <c r="AL6" s="73"/>
+      <c r="AM6" s="73"/>
+      <c r="AN6" s="73"/>
+      <c r="AO6" s="73"/>
+      <c r="AP6" s="73"/>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" s="105" t="s">
@@ -21962,181 +21742,181 @@
       <c r="A8" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="72"/>
-      <c r="X8" s="72"/>
-      <c r="Y8" s="72"/>
-      <c r="Z8" s="72"/>
-      <c r="AA8" s="72"/>
-      <c r="AB8" s="72"/>
-      <c r="AC8" s="72"/>
-      <c r="AD8" s="72"/>
-      <c r="AE8" s="72"/>
-      <c r="AF8" s="72"/>
-      <c r="AG8" s="72"/>
-      <c r="AH8" s="72"/>
-      <c r="AI8" s="72"/>
-      <c r="AJ8" s="72"/>
-      <c r="AK8" s="72"/>
-      <c r="AL8" s="72"/>
-      <c r="AM8" s="72"/>
-      <c r="AN8" s="72"/>
-      <c r="AO8" s="72"/>
-      <c r="AP8" s="72"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="73"/>
+      <c r="S8" s="73"/>
+      <c r="T8" s="73"/>
+      <c r="U8" s="73"/>
+      <c r="V8" s="73"/>
+      <c r="W8" s="73"/>
+      <c r="X8" s="73"/>
+      <c r="Y8" s="73"/>
+      <c r="Z8" s="73"/>
+      <c r="AA8" s="73"/>
+      <c r="AB8" s="73"/>
+      <c r="AC8" s="73"/>
+      <c r="AD8" s="73"/>
+      <c r="AE8" s="73"/>
+      <c r="AF8" s="73"/>
+      <c r="AG8" s="73"/>
+      <c r="AH8" s="73"/>
+      <c r="AI8" s="73"/>
+      <c r="AJ8" s="73"/>
+      <c r="AK8" s="73"/>
+      <c r="AL8" s="73"/>
+      <c r="AM8" s="73"/>
+      <c r="AN8" s="73"/>
+      <c r="AO8" s="73"/>
+      <c r="AP8" s="73"/>
     </row>
     <row r="9" spans="1:42">
       <c r="A9" s="108"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="72"/>
-      <c r="V9" s="72"/>
-      <c r="W9" s="72"/>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="72"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="72"/>
-      <c r="AC9" s="72"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="72"/>
-      <c r="AF9" s="72"/>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="72"/>
-      <c r="AJ9" s="72"/>
-      <c r="AK9" s="72"/>
-      <c r="AL9" s="72"/>
-      <c r="AM9" s="72"/>
-      <c r="AN9" s="72"/>
-      <c r="AO9" s="72"/>
-      <c r="AP9" s="72"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="73"/>
+      <c r="T9" s="73"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="73"/>
+      <c r="Y9" s="73"/>
+      <c r="Z9" s="73"/>
+      <c r="AA9" s="73"/>
+      <c r="AB9" s="73"/>
+      <c r="AC9" s="73"/>
+      <c r="AD9" s="73"/>
+      <c r="AE9" s="73"/>
+      <c r="AF9" s="73"/>
+      <c r="AG9" s="73"/>
+      <c r="AH9" s="73"/>
+      <c r="AI9" s="73"/>
+      <c r="AJ9" s="73"/>
+      <c r="AK9" s="73"/>
+      <c r="AL9" s="73"/>
+      <c r="AM9" s="73"/>
+      <c r="AN9" s="73"/>
+      <c r="AO9" s="73"/>
+      <c r="AP9" s="73"/>
     </row>
     <row r="10" spans="1:42" ht="23.25" customHeight="1">
-      <c r="A10" s="109" t="s">
+      <c r="A10" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="72"/>
-      <c r="AB10" s="72"/>
-      <c r="AC10" s="72"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="72"/>
-      <c r="AJ10" s="72"/>
-      <c r="AK10" s="72"/>
-      <c r="AL10" s="72"/>
-      <c r="AM10" s="72"/>
-      <c r="AN10" s="72"/>
-      <c r="AO10" s="72"/>
-      <c r="AP10" s="72"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="73"/>
+      <c r="T10" s="73"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="73"/>
+      <c r="AC10" s="73"/>
+      <c r="AD10" s="73"/>
+      <c r="AE10" s="73"/>
+      <c r="AF10" s="73"/>
+      <c r="AG10" s="73"/>
+      <c r="AH10" s="73"/>
+      <c r="AI10" s="73"/>
+      <c r="AJ10" s="73"/>
+      <c r="AK10" s="73"/>
+      <c r="AL10" s="73"/>
+      <c r="AM10" s="73"/>
+      <c r="AN10" s="73"/>
+      <c r="AO10" s="73"/>
+      <c r="AP10" s="73"/>
     </row>
     <row r="11" spans="1:42" ht="15.75">
-      <c r="A11" s="109"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="72"/>
-      <c r="AB11" s="72"/>
-      <c r="AC11" s="72"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="72"/>
-      <c r="AF11" s="72"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="72"/>
-      <c r="AJ11" s="72"/>
-      <c r="AK11" s="72"/>
-      <c r="AL11" s="72"/>
-      <c r="AM11" s="72"/>
-      <c r="AN11" s="72"/>
-      <c r="AO11" s="72"/>
-      <c r="AP11" s="72"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
+      <c r="Q11" s="73"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="73"/>
+      <c r="T11" s="73"/>
+      <c r="U11" s="73"/>
+      <c r="V11" s="73"/>
+      <c r="W11" s="73"/>
+      <c r="X11" s="73"/>
+      <c r="Y11" s="73"/>
+      <c r="Z11" s="73"/>
+      <c r="AA11" s="73"/>
+      <c r="AB11" s="73"/>
+      <c r="AC11" s="73"/>
+      <c r="AD11" s="73"/>
+      <c r="AE11" s="73"/>
+      <c r="AF11" s="73"/>
+      <c r="AG11" s="73"/>
+      <c r="AH11" s="73"/>
+      <c r="AI11" s="73"/>
+      <c r="AJ11" s="73"/>
+      <c r="AK11" s="73"/>
+      <c r="AL11" s="73"/>
+      <c r="AM11" s="73"/>
+      <c r="AN11" s="73"/>
+      <c r="AO11" s="73"/>
+      <c r="AP11" s="73"/>
     </row>
     <row r="12" spans="1:42" ht="30" customHeight="1">
       <c r="A12" s="31" t="s">
@@ -22242,11 +22022,11 @@
       <c r="AI12" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="AJ12" s="110" t="s">
+      <c r="AJ12" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="AK12" s="111"/>
-      <c r="AL12" s="112"/>
+      <c r="AK12" s="95"/>
+      <c r="AL12" s="96"/>
       <c r="AM12" s="33" t="s">
         <v>58</v>
       </c>
@@ -22396,11 +22176,11 @@
       <c r="AI13" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="AJ13" s="93" t="s">
+      <c r="AJ13" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="AK13" s="94"/>
-      <c r="AL13" s="95"/>
+      <c r="AK13" s="101"/>
+      <c r="AL13" s="102"/>
       <c r="AM13" s="37">
         <f>SUM(February!AH14)</f>
         <v>0</v>
@@ -22552,11 +22332,11 @@
       </c>
       <c r="AH14" s="29"/>
       <c r="AI14" s="114"/>
-      <c r="AJ14" s="96" t="s">
+      <c r="AJ14" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="AK14" s="97"/>
-      <c r="AL14" s="98"/>
+      <c r="AK14" s="98"/>
+      <c r="AL14" s="99"/>
       <c r="AM14" s="39">
         <f>SUM(February!AH19)</f>
         <v>0</v>
@@ -22707,11 +22487,11 @@
       <c r="AI15" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="AJ15" s="93" t="s">
+      <c r="AJ15" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="AK15" s="94"/>
-      <c r="AL15" s="95"/>
+      <c r="AK15" s="101"/>
+      <c r="AL15" s="102"/>
       <c r="AM15" s="37">
         <f>SUM(February!AH24)</f>
         <v>0</v>
@@ -22863,11 +22643,11 @@
       </c>
       <c r="AH16" s="29"/>
       <c r="AI16" s="117"/>
-      <c r="AJ16" s="99" t="s">
+      <c r="AJ16" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="AK16" s="77"/>
-      <c r="AL16" s="68"/>
+      <c r="AK16" s="70"/>
+      <c r="AL16" s="66"/>
       <c r="AM16" s="41">
         <f>SUM(February!AH29)</f>
         <v>0</v>
@@ -22920,11 +22700,11 @@
       </c>
       <c r="J17" s="35">
         <f>SUM(February!K84,February!K85,February!K89,February!K90,February!K94,February!K95)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="35">
         <f>SUM(February!L84,February!L85,February!L89,February!L90,February!L94,February!L95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="35">
         <f>SUM(February!M84,February!M85,February!M89,February!M90,February!M94,February!M95)</f>
@@ -22936,7 +22716,7 @@
       </c>
       <c r="N17" s="35">
         <f>SUM(February!O84,February!O85,February!O89,February!O90,February!O94,February!O95)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" s="35">
         <f>SUM(February!P84,February!P85,February!P89,February!P90,February!P94,February!P95)</f>
@@ -22948,11 +22728,11 @@
       </c>
       <c r="Q17" s="35">
         <f>SUM(February!R84,February!R85,February!R89,February!R90,February!R94,February!R95)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" s="35">
         <f>SUM(February!S84,February!S85,February!S89,February!S90,February!S94,February!S95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="35">
         <f>SUM(February!T84,February!T85,February!T89,February!T90,February!T94,February!T95)</f>
@@ -22980,11 +22760,11 @@
       </c>
       <c r="Y17" s="35">
         <f>SUM(February!Z84,February!Z85,February!Z89,February!Z90,February!Z94,February!Z95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="35">
         <f>SUM(February!AA84,February!AA85,February!AA89,February!AA90,February!AA94,February!AA95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="35">
         <f>SUM(February!AB84,February!AB85,February!AB89,February!AB90,February!AB94,February!AB95)</f>
@@ -23012,15 +22792,15 @@
       </c>
       <c r="AG17" s="36">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="29"/>
       <c r="AI17" s="117"/>
-      <c r="AJ17" s="99" t="s">
+      <c r="AJ17" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="AK17" s="77"/>
-      <c r="AL17" s="68"/>
+      <c r="AK17" s="70"/>
+      <c r="AL17" s="66"/>
       <c r="AM17" s="41">
         <f>SUM(February!AH34)</f>
         <v>0</v>
@@ -23169,11 +22949,11 @@
       </c>
       <c r="AH18" s="29"/>
       <c r="AI18" s="114"/>
-      <c r="AJ18" s="96" t="s">
+      <c r="AJ18" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="AK18" s="97"/>
-      <c r="AL18" s="98"/>
+      <c r="AK18" s="98"/>
+      <c r="AL18" s="99"/>
       <c r="AM18" s="39">
         <f>SUM(February!AH39)</f>
         <v>0</v>
@@ -23324,11 +23104,11 @@
       <c r="AI19" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="AJ19" s="93" t="s">
+      <c r="AJ19" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="AK19" s="94"/>
-      <c r="AL19" s="95"/>
+      <c r="AK19" s="101"/>
+      <c r="AL19" s="102"/>
       <c r="AM19" s="37">
         <f>SUM(February!AH44)</f>
         <v>0</v>
@@ -23384,11 +23164,11 @@
       </c>
       <c r="J20" s="44">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="44">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="44">
         <f t="shared" si="1"/>
@@ -23400,7 +23180,7 @@
       </c>
       <c r="N20" s="44">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="44">
         <f t="shared" si="1"/>
@@ -23412,11 +23192,11 @@
       </c>
       <c r="Q20" s="44">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" s="44">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="44">
         <f t="shared" si="1"/>
@@ -23444,11 +23224,11 @@
       </c>
       <c r="Y20" s="44">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="44">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="44">
         <f t="shared" si="1"/>
@@ -23476,15 +23256,15 @@
       </c>
       <c r="AG20" s="45">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="29"/>
       <c r="AI20" s="117"/>
-      <c r="AJ20" s="99" t="s">
+      <c r="AJ20" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="AK20" s="77"/>
-      <c r="AL20" s="68"/>
+      <c r="AK20" s="70"/>
+      <c r="AL20" s="66"/>
       <c r="AM20" s="41">
         <f>SUM(February!AH49)</f>
         <v>0</v>
@@ -23535,11 +23315,11 @@
       <c r="AG21" s="120"/>
       <c r="AH21" s="29"/>
       <c r="AI21" s="114"/>
-      <c r="AJ21" s="96" t="s">
+      <c r="AJ21" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="AK21" s="97"/>
-      <c r="AL21" s="98"/>
+      <c r="AK21" s="98"/>
+      <c r="AL21" s="99"/>
       <c r="AM21" s="39">
         <f>SUM(February!AH54)</f>
         <v>0</v>
@@ -23593,11 +23373,11 @@
       <c r="AI22" s="121" t="s">
         <v>82</v>
       </c>
-      <c r="AJ22" s="93" t="s">
+      <c r="AJ22" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="AK22" s="94"/>
-      <c r="AL22" s="95"/>
+      <c r="AK22" s="101"/>
+      <c r="AL22" s="102"/>
       <c r="AM22" s="37">
         <f>SUM(February!AH59)</f>
         <v>0</v>
@@ -23651,11 +23431,11 @@
       <c r="AG23" s="47"/>
       <c r="AH23" s="29"/>
       <c r="AI23" s="117"/>
-      <c r="AJ23" s="99" t="s">
+      <c r="AJ23" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="AK23" s="77"/>
-      <c r="AL23" s="68"/>
+      <c r="AK23" s="70"/>
+      <c r="AL23" s="66"/>
       <c r="AM23" s="41">
         <f>SUM(February!AH64)</f>
         <v>0</v>
@@ -23671,11 +23451,11 @@
       <c r="AP23" s="117"/>
     </row>
     <row r="24" spans="1:42" ht="30" customHeight="1">
-      <c r="A24" s="82" t="s">
+      <c r="A24" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
       <c r="D24" s="23"/>
       <c r="E24" s="46"/>
       <c r="F24" s="46"/>
@@ -23708,11 +23488,11 @@
       <c r="AG24" s="47"/>
       <c r="AH24" s="29"/>
       <c r="AI24" s="117"/>
-      <c r="AJ24" s="99" t="s">
+      <c r="AJ24" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="AK24" s="77"/>
-      <c r="AL24" s="68"/>
+      <c r="AK24" s="70"/>
+      <c r="AL24" s="66"/>
       <c r="AM24" s="41">
         <f>SUM(February!AH69)</f>
         <v>0</v>
@@ -23731,7 +23511,7 @@
       <c r="A25" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="72"/>
+      <c r="B25" s="73"/>
       <c r="C25" s="49"/>
       <c r="D25" s="23"/>
       <c r="E25" s="46"/>
@@ -23765,11 +23545,11 @@
       <c r="AG25" s="47"/>
       <c r="AH25" s="29"/>
       <c r="AI25" s="117"/>
-      <c r="AJ25" s="99" t="s">
+      <c r="AJ25" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="AK25" s="77"/>
-      <c r="AL25" s="68"/>
+      <c r="AK25" s="70"/>
+      <c r="AL25" s="66"/>
       <c r="AM25" s="41">
         <f>SUM(February!AH74)</f>
         <v>0</v>
@@ -23820,11 +23600,11 @@
       <c r="AG26" s="47"/>
       <c r="AH26" s="29"/>
       <c r="AI26" s="114"/>
-      <c r="AJ26" s="96" t="s">
+      <c r="AJ26" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="AK26" s="97"/>
-      <c r="AL26" s="98"/>
+      <c r="AK26" s="98"/>
+      <c r="AL26" s="99"/>
       <c r="AM26" s="39">
         <f>SUM(February!AH79)</f>
         <v>0</v>
@@ -23879,11 +23659,11 @@
       <c r="AI27" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="AJ27" s="93" t="s">
+      <c r="AJ27" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="AK27" s="94"/>
-      <c r="AL27" s="95"/>
+      <c r="AK27" s="101"/>
+      <c r="AL27" s="102"/>
       <c r="AM27" s="37">
         <f>SUM(February!AH84)</f>
         <v>0</v>
@@ -23898,7 +23678,7 @@
       </c>
       <c r="AP27" s="115">
         <f>SUM(AO27,AO28,AO29)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="30" customHeight="1">
@@ -23937,34 +23717,34 @@
       <c r="AG28" s="47"/>
       <c r="AH28" s="29"/>
       <c r="AI28" s="117"/>
-      <c r="AJ28" s="99" t="s">
+      <c r="AJ28" s="103" t="s">
         <v>92</v>
       </c>
-      <c r="AK28" s="77"/>
-      <c r="AL28" s="68"/>
+      <c r="AK28" s="70"/>
+      <c r="AL28" s="66"/>
       <c r="AM28" s="41">
         <f>SUM(February!AH89)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="41">
         <f>SUM(February!AH90)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="42">
         <f>SUM(February!AH89,February!AH90)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AP28" s="117"/>
     </row>
     <row r="29" spans="1:42" ht="30" customHeight="1">
-      <c r="A29" s="82" t="s">
+      <c r="A29" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
       <c r="G29" s="51"/>
       <c r="H29" s="52"/>
       <c r="I29" s="52"/>
@@ -23994,11 +23774,11 @@
       <c r="AG29" s="47"/>
       <c r="AH29" s="29"/>
       <c r="AI29" s="114"/>
-      <c r="AJ29" s="96" t="s">
+      <c r="AJ29" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="AK29" s="97"/>
-      <c r="AL29" s="98"/>
+      <c r="AK29" s="98"/>
+      <c r="AL29" s="99"/>
       <c r="AM29" s="39">
         <f>SUM(February!AH94)</f>
         <v>0</v>
@@ -24017,9 +23797,9 @@
       <c r="A30" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
       <c r="E30" s="26"/>
       <c r="F30" s="50"/>
       <c r="G30" s="51"/>
@@ -24053,11 +23833,11 @@
       <c r="AI30" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="AJ30" s="93" t="s">
+      <c r="AJ30" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="AK30" s="94"/>
-      <c r="AL30" s="95"/>
+      <c r="AK30" s="101"/>
+      <c r="AL30" s="102"/>
       <c r="AM30" s="37">
         <f>SUM(February!AH100)</f>
         <v>0</v>
@@ -24171,21 +23951,21 @@
       <c r="AJ32" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="AK32" s="111"/>
-      <c r="AL32" s="112"/>
+      <c r="AK32" s="95"/>
+      <c r="AL32" s="96"/>
       <c r="AM32" s="57">
         <f t="shared" ref="AM32:AO32" si="2">SUM(AM13:AM31)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="57">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="126">
         <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="AP32" s="112"/>
+        <v>0</v>
+      </c>
+      <c r="AP32" s="96"/>
     </row>
     <row r="33" spans="1:42" ht="30.75" customHeight="1">
       <c r="A33" s="26"/>
@@ -24232,11 +24012,11 @@
       <c r="AP33" s="58"/>
     </row>
     <row r="34" spans="1:42" ht="30" customHeight="1">
-      <c r="A34" s="82" t="s">
+      <c r="A34" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="50"/>
@@ -24268,14 +24048,14 @@
       <c r="AF34" s="59"/>
       <c r="AG34" s="59"/>
       <c r="AH34" s="29"/>
-      <c r="AI34" s="131" t="s">
+      <c r="AI34" s="127" t="s">
         <v>96</v>
       </c>
-      <c r="AJ34" s="94"/>
-      <c r="AK34" s="94"/>
-      <c r="AL34" s="94"/>
-      <c r="AM34" s="94"/>
-      <c r="AN34" s="132"/>
+      <c r="AJ34" s="101"/>
+      <c r="AK34" s="101"/>
+      <c r="AL34" s="101"/>
+      <c r="AM34" s="101"/>
+      <c r="AN34" s="128"/>
       <c r="AO34" s="58"/>
       <c r="AP34" s="58"/>
     </row>
@@ -24283,8 +24063,8 @@
       <c r="A35" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="50"/>
@@ -24316,27 +24096,27 @@
       <c r="AF35" s="59"/>
       <c r="AG35" s="59"/>
       <c r="AH35" s="29"/>
-      <c r="AI35" s="127" t="s">
+      <c r="AI35" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="AJ35" s="77"/>
-      <c r="AK35" s="77"/>
-      <c r="AL35" s="68"/>
+      <c r="AJ35" s="70"/>
+      <c r="AK35" s="70"/>
+      <c r="AL35" s="66"/>
       <c r="AM35" s="60">
         <f>SUM(February!AH14,February!AH19,February!AH24,February!AH29,February!AH34,February!AH39,February!AH44,February!AH49,February!AH54,February!AH59,February!AH64,February!AH69,February!AH74,February!AH79,February!AH84,February!AH89,February!AH94,February!AH100,February!AH105)</f>
-        <v>7</v>
-      </c>
-      <c r="AN35" s="128">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="130">
         <f>SUM(AM35,AM36)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AO35" s="51"/>
       <c r="AP35" s="51"/>
     </row>
     <row r="36" spans="1:42" ht="30" customHeight="1">
       <c r="A36" s="75"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
       <c r="D36" s="49"/>
       <c r="E36" s="49"/>
       <c r="F36" s="46"/>
@@ -24368,24 +24148,24 @@
       <c r="AF36" s="59"/>
       <c r="AG36" s="59"/>
       <c r="AH36" s="29"/>
-      <c r="AI36" s="130" t="s">
+      <c r="AI36" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="AJ36" s="97"/>
-      <c r="AK36" s="97"/>
-      <c r="AL36" s="98"/>
+      <c r="AJ36" s="98"/>
+      <c r="AK36" s="98"/>
+      <c r="AL36" s="99"/>
       <c r="AM36" s="61">
         <f>SUM(February!AH15,February!AH20,February!AH25,February!AH30,February!AH35,February!AH40,February!AH45,February!AH50,February!AH55,February!AH60,February!AH65,February!AH70,February!AH75,February!AH80,February!AH85,February!AH90,February!AH95,February!AH101,February!AH106)</f>
-        <v>6</v>
-      </c>
-      <c r="AN36" s="129"/>
+        <v>0</v>
+      </c>
+      <c r="AN36" s="131"/>
       <c r="AO36" s="51"/>
       <c r="AP36" s="51"/>
     </row>
     <row r="37" spans="1:42" ht="30" customHeight="1">
       <c r="A37" s="75"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
       <c r="D37" s="49"/>
       <c r="E37" s="49"/>
       <c r="F37" s="46"/>
@@ -35321,15 +35101,11 @@
     <mergeCell ref="AP15:AP18"/>
     <mergeCell ref="AP19:AP21"/>
     <mergeCell ref="AP22:AP26"/>
-    <mergeCell ref="AI13:AI14"/>
-    <mergeCell ref="AP13:AP14"/>
-    <mergeCell ref="AI15:AI18"/>
-    <mergeCell ref="AI19:AI21"/>
-    <mergeCell ref="A21:AG21"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:AP2"/>
     <mergeCell ref="A3:AP3"/>
@@ -35345,13 +35121,17 @@
     <mergeCell ref="AJ18:AL18"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AJ13:AL13"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AI15:AI18"/>
+    <mergeCell ref="AI19:AI21"/>
+    <mergeCell ref="A21:AG21"/>
+    <mergeCell ref="AJ21:AL21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
